--- a/Libraries/Vehicle/AntiRollBar/sm_car_data_AntiRollBar_Droplink_Rod_Lever4Points.xlsx
+++ b/Libraries/Vehicle/AntiRollBar/sm_car_data_AntiRollBar_Droplink_Rod_Lever4Points.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\AntiRollBar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B460AF3-6B5D-48AF-9F9A-E8804ACEB647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBBA36EE-6FEA-4BEC-989A-7BF28B4E3BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="979" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" tabRatio="979" xr2:uid="{3FA59F9D-D9D3-4E28-B3CE-9BFC80E89258}"/>
   </bookViews>
   <sheets>
     <sheet name="Sedan_Hamba_LA_f" sheetId="20" r:id="rId1"/>
@@ -112,9 +112,6 @@
     <t>deg</t>
   </si>
   <si>
-    <t>DroplinkRod_Sedan_Hamba_LA_r</t>
-  </si>
-  <si>
     <t>sLever4</t>
   </si>
   <si>
@@ -131,6 +128,9 @@
   </si>
   <si>
     <t>DroplinkRodLever4Points_Sedan_Hamba_LA_f</t>
+  </si>
+  <si>
+    <t>DroplinkRodLever4Points_Sedan_Hamba_LA_r</t>
   </si>
 </sst>
 </file>
@@ -664,7 +664,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -678,7 +678,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -728,7 +728,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -748,7 +748,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -768,7 +768,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -788,7 +788,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1041,7 +1041,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="7" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1055,7 +1055,7 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1105,7 +1105,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1165,7 +1165,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
